--- a/光伏配储项目/电价数据/2026/昆山站.xlsx
+++ b/光伏配储项目/电价数据/2026/昆山站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.51181</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38459</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.7614099999999999</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.5746</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.5738799999999999</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.51115</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.51664</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43313</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.44921</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.42387</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.4176</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.41664</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40508</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.3945</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39362</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.3821</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.39763</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.41829</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.40857</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.3527</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.38839</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38215</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41345</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.38919</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.41707</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41049</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.4203</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.40895</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.43829</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.48627</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.39364</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31176</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32662</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.34789</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.37012</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32293</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.26357</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.25499</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.02687</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.18026</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.25659</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.02025</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.11739</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.13035</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.19892</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.20399</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.18816</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>-0.041</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.29161</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.19815</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.15562</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.45145</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.56471</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.51986</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.73358</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.09148</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.3949</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.00975</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43193</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43738</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.66028</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.83368</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.44242</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.16724</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.60844</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.05118</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.25103</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.40706</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.6523099999999999</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.7034</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.20663</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.01774</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.8784299999999999</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.79862</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.7595299999999999</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.5182</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48162</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.46965</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41675</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42652</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.7135199999999999</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.79726</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.8786</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.92698</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.4981</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5201399999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5063299999999999</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50656</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48862</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40111</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.4704100000000001</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37935</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.40363</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33677</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37335</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35886</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35876</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.38573</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.38098</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.36662</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38486</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.42797</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>1.01928</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.94512</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.47467</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.46309</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.37881</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34813</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.38355</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.42184</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.50671</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.35263</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.32391</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35692</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.2568</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.246</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.31315</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29933</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.30142</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.19579</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.12694</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.31211</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.61085</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.8079</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.13824</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.25136</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.80671</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.7393</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.22293</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.31464</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.66486</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.94396</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>-0.00051</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.28555</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.38318</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.42367</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.39829</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.4845</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.7565499999999999</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.6217</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.7643300000000001</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.78034</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.15923</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.24606</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.17339</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.8499800000000001</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.20357</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.1046</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.25696</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.03111</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.08944</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.6463099999999999</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.98238</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.9077200000000001</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.96689</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.82578</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.9311200000000001</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.76606</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.75714</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.4515</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.7586900000000001</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.78235</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.45035</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42924</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44488</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33376</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37653</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33478</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.51084</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.48969</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.49036</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37814</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.44918</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41569</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.3699</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39054</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38408</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36412</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42993</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44573</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33619</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.3712</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39728</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.3681</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36889</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35661</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36219</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.3525</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.37112</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.36145</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38703</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39756</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47518</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44543</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44006</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34764</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39562</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35335</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36723</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34758</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.46615</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.4507</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.28841</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.36105</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.11855</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.42848</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.01995</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.32785</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.03565</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.24519</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.12528</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.63127</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.30163</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.56441</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.6343099999999999</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.49884</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.38826</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.80233</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.58402</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.58765</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.46306</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.465</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.06196</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.43099</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.3943</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.46605</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.47048</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.47586</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.54688</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.5495399999999999</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.48568</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.5079</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.27971</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.61942</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.62051</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.4638</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.5064</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.50806</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.59372</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.54983</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.62207</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.44353</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.42427</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.48471</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.6145700000000001</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.61771</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.56096</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.74694</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.62695</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.5422</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.45388</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.58872</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.44283</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45789</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39804</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36204</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34882</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34215</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.52428</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.49598</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.44636</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.3904</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.39033</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.39958</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36787</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35968</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.3886</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38669</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36226</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.45063</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.3607</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.3492</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36392</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35821</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35933</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33788</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33537</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33193</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33161</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35039</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38609</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38956</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34905</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37558</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34436</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39394</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.41658</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.42751</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35644</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.40534</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34062</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.34084</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.22374</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.19706</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.28296</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.28571</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.2018</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.30872</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.60768</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.53228</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.44175</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.35269</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.19642</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.26114</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.42817</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.34211</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.35408</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.33517</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.41925</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.6111599999999999</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.3352</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.32074</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34774</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.46676</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.39157</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.40078</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.28708</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.30738</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.31485</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.47473</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.48545</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.43769</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.5016499999999999</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45023</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.4646</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.47511</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.5054</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.56489</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.44061</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.55531</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.47756</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.46048</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50069</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.42297</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.40287</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.39689</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.41807</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.36212</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34683</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34194</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32332</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31414</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31846</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.32074</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.3211</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.41429</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.39399</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38199</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34108</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.3291</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32804</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33214</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32074</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31902</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31609</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31881</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31851</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31514</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31641</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31293</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31432</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31944</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31605</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.31076</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.31012</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31339</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31468</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.32112</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.32244</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.33267</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.35507</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.3127</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.33074</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.32577</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.23197</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.3038</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.30495</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.15456</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.29716</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.20784</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.1505</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.23184</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.01445</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.16462</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.30352</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.3023</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.14748</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.10866</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.13385</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>-0.01315</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.00671</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.26825</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29753</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29991</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.2941</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30169</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33572</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.3369</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.39681</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.4002</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.3963</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.38185</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.36209</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.40866</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.40666</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.41755</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.47263</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.40138</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40646</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.51327</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35715</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35919</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.3451</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35601</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35653</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36874</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.71045</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.41659</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.48004</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.45235</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.45595</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.36553</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.37064</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.36235</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.35603</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.31474</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.35274</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.37331</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.42294</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.35214</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.35144</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33997</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.33937</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.34354</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.35513</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30588</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.34683</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.34026</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.35361</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.36315</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35696</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.36577</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.32409</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10242</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04336</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.0441</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04475</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.36015</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01571</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.21706</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.05467</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.29143</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.20243</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04272</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04529</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04423</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.07121</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.06945</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29329</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29678</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34784</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35124</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34754</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.37086</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36854</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33867</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33494</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31881</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.41175</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35366</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32086</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27071</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30939</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29732</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38044</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37998</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.4284</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45675</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41845</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41528</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38982</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40242</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29431</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31269</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34628</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38546</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.7853600000000001</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142100000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.8628899999999999</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29622</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35366</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88751</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18709</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8683500000000001</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.5152599999999999</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33086</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03292</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53079</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79099</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5252899999999999</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77298</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77755</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87387</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49316</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.3999</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44995</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.207</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62186</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49769</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45582</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45006</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41984</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35576</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40112</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36713</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38613</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41919</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43956</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34712</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39273</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35431</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33371</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.3487</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.4172</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34745</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45189</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35913</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40609</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.41291</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.60827</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.45296</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.60454</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.75685</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.88026</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46925</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.4394</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.60412</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.46374</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.9215399999999999</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.6748500000000001</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.8651799999999999</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87498</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34789</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.46104</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.75274</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30796</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.30666</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.73734</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.59811</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.30432</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31056</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.36027</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33463</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.3395899999999999</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31844</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31915</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.32017</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.35056</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31365</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32145</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30537</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29585</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31297</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31679</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31323</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.33758</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.31799</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.32381</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32978</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.33353</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35927</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34864</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34521</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.3431</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33539</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.34462</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.3424</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.42789</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.43092</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.47617</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.43362</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.40585</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.38909</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35841</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9234199999999999</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36921</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.48237</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.44356</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.42208</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.48893</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.39237</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.42594</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.36834</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.37419</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.35643</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35379</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.35486</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.36788</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.35308</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32735</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.41816</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.53073</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.3659</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.40273</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.35116</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35967</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.36488</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.38283</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.36767</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.37295</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.32303</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.3173</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.34448</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.34341</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.35672</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31689</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31441</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29186</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.3128</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.2719</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.29371</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.14555</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30431</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30873</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.32419</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.32489</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.31751</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.27139</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19944</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.3087</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29875</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.32333</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.28451</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.3124</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31281</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.35445</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.36391</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.3178</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31807</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.32616</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.32243</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.37647</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.32102</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.32004</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.30267</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.3147799999999999</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32842</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31783</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29066</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.35628</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25643</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35892</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32874</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.34162</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27733</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.33491</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.34851</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31585</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.35911</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.34277</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.39803</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.35714</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.46769</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35334</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.34816</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42443</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35803</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.45648</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.34637</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.43563</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.36445</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.41819</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.41772</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.64707</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.37231</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.90566</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.47488</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.17138</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.70812</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79923</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.65913</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.64093</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.49029</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45763</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50817</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.44696</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.45403</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.42205</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41932</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.43864</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5317200000000001</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41922</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.44074</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.43245</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.44069</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39584</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.4515</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.47754</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.40246</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42956</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.45812</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.4192</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41823</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.41889</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.44754</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.40472</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.4223</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.5010599999999999</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.36799</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.37667</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.38399</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.37903</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.3147799999999999</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.34833</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30998</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.32398</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30726</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.57368</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.36937</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.37786</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.25022</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.30859</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.16031</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.28244</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27624</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.00223</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.34225</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30132</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26235</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25633</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30826</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28338</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.29066</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.29749</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29376</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.31344</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31574</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.32783</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.3487</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.34842</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.41633</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.41332</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.3559</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.36612</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.34684</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.37455</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.34803</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.37643</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.3732</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.3681</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.35473</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.5929</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.48592</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.89177</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.48931</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.46154</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.38893</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.47622</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.39779</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.37857</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.34035</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.35252</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.33522</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.33619</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.4484</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.3532</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.36905</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.3486</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.35167</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.34978</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.3469</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.35195</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.32253</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.33943</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.3381</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.32044</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.34847</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.34835</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.31539</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31589</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.37871</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.34351</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.4245</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.38571</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.37462</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.43424</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.40698</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.36356</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.34345</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.37425</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.34183</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.36444</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.32371</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.31694</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.34092</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.33765</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.32812</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.30186</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.29138</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.22299</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.1194</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.12507</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.27879</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.13375</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.12219</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.12293</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.25841</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.12674</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.24165</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.25316</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.28582</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.17976</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.09994</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.07922</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.09974</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.10344</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.18522</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.11875</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.27793</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.32374</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.33209</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.32615</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.36177</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.36481</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.35837</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.37829</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.3921</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.35406</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.41382</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.3715</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.39935</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.47495</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.41679</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.40554</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.41886</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.41312</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.48037</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.46757</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.46584</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.47128</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44958</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40836</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39632</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.40326</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39707</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.37349</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.3737</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.36632</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.36163</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.34852</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5823200000000001</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.39435</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.49908</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.44569</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.43663</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.38403</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.39656</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.3944</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.40937</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.38522</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.3757799999999999</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.39433</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.37088</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.40759</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.38324</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.3964</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.36075</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.35726</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.3544</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34906</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.35478</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34906</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.47924</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.38485</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.39593</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.3719</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34799</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.33446</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35687</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.36715</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.30086</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31815</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.3134</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30973</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29732</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.27903</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.27025</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.26867</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.21747</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.31549</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.25387</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.23427</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.13743</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30087</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30227</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31902</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31728</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.1731</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.20844</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31454</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.30344</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.28397</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24676</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.3202</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.31208</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.33109</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.3410899999999999</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.31644</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.57628</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.35378</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.38582</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.35453</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.34664</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.3484</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.3953</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.38944</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35803</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.35286</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.36232</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.38469</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.44718</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.39674</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.38564</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.29256</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.38357</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38837</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.36436</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.36855</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.36589</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.43627</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.3519</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.35627</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.37781</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.37936</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.36881</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.39821</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.39439</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.39974</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35867</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.37086</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34394</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.37709</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.54399</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37624</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.55414</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.39367</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.36199</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.38597</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.37285</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.36414</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.35116</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.35487</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.35915</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.35239</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.35231</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.35085</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34859</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.34405</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.34676</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34538</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.3410899999999999</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34954</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.35251</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.39791</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.38565</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.39648</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.38664</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.34217</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.35023</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.35954</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.3621</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.41646</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.19206</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.38999</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.6825399999999999</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.38167</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.47177</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.44861</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.36669</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.41305</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.51518</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.37953</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.42709</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.38878</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.30363</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.24556</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.28923</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.36933</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.20296</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.71193</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.21985</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.34221</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.35728</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.32951</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.47253</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.36636</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.09265999999999999</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.40786</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.43048</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.40481</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.35185</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.40186</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.36623</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.32608</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.41897</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.32983</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.33512</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.61346</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.46335</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.39224</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.44639</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.42829</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.70125</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.37266</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.8497400000000001</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.74959</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.62071</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.3804</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.51586</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.25527</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.38862</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.35467</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.34662</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.33808</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.35242</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.34232</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.36566</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.46569</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.36921</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.37425</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.45645</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.42571</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.36427</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.34527</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.3627</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.38883</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.3737</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.35715</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.34694</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.35629</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.34135</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.34192</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.34069</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.33711</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.36101</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.35831</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.35954</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.33725</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.32567</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32884</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.33889</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.35804</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.36241</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.3719</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.37938</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.38636</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.36938</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.37724</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.34963</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.35232</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.36151</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.38572</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.38547</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.3407</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.37421</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.39865</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.35471</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.33012</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.35522</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.33786</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.35495</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.35475</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.3225</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.34556</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28949</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.34386</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.32323</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32895</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.33173</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.33425</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.34052</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.35034</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.33646</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.33103</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.32874</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32846</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.3657</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.36173</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.35436</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.40587</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.37876</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.3819</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.35491</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.36093</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35715</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35918</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.39828</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.34292</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.38824</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36992</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36183</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.38002</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36302</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.38433</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.40596</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.40456</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37757</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.43208</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.39981</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.37088</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.39101</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.38663</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35588</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.37175</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.35548</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.34876</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35623</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35523</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35624</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35667</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.36284</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.35524</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.35209</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.43311</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.35287</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.36194</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.34542</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34587</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.38607</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.3491</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.34542</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.36231</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.34667</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.35261</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.35087</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.34597</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.36111</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.36121</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.34218</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.33888</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.36113</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.34302</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.34675</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.31617</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.33328</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.33402</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.33399</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32667</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.32185</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32998</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31978</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.33317</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32964</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32857</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31751</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36966</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32523</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.36085</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.3975</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.33274</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32816</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.33161</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.34639</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.35234</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.34766</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.34075</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.36626</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.36757</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.3633</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.36546</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.37278</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35569</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.36848</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.35269</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.3673</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.3646</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36718</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35455</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.39293</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.39516</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.39363</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.3963</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.44601</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.41951</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38163</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6622899999999999</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47465</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.31336</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.48619</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.44549</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35621</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.3642</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.34462</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.35242</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32206</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.4185</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.38364</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.38273</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.3694</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.36654</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.36621</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36937</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.36547</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.3714</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.36633</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36734</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.37214</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.36348</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.3711</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36683</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.36716</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.39211</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.36613</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.36387</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36743</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36743</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.39635</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.37323</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.38724</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.36392</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.36383</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35854</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35923</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.36527</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.35716</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33516</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.33789</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.25879</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.29887</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.17629</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.1718</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.17006</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.15557</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.20074</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.20216</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.26946</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.19209</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.24024</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.27495</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.26646</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.29721</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.28424</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30161</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.31305</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.39206</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.30205</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29883</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.29764</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32656</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.34629</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.34259</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.33678</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.34802</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.3322</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.31686</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33309</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.36543</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.35308</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.37591</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.38392</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.46748</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.39781</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.4243</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.65434</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.61222</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.6171</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.54503</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.8211000000000001</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.53108</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.94664</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.50859</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.49918</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.41072</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.37481</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.38109</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.5203099999999999</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.45828</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.44422</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.39282</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.38208</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.37962</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.37131</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34576</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.52406</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.62906</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.55455</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.76349</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.43773</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.43871</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.42072</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.43043</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.42682</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.43738</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.41563</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.40104</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.427</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.42481</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.40861</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.39434</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.44251</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.40506</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.44025</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.42461</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.42111</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.43481</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.42264</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.48729</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.48232</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.61839</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.54252</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.48108</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.5366599999999999</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.47842</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.47578</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.40898</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.39389</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.45609</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.49263</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.48927</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.5727300000000001</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.44079</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.39204</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.36168</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.37287</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.43012</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.41986</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.42267</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.36948</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.29995</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.33066</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.32179</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.40094</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.65051</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.41486</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.86117</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.38484</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.39013</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.40725</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.37794</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.3865</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33929</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.30422</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33593</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.36079</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.38381</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.36552</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.38611</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.38997</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.40072</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.36262</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.40195</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.34437</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.4327</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.46103</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.52862</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.47915</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.55401</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.55562</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.60476</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.78587</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.9535800000000001</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.04988</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.74701</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.90843</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.76934</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.59601</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.94024</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.77671</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.62986</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.67887</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.49793</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.5201</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.51859</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.5108199999999999</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.5032799999999999</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.43794</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.60109</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.45118</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.46804</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.48575</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.4408</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.43072</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.47391</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.42246</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.41776</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.49611</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.42155</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.42929</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.41268</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.4029700000000001</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.3918</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.38782</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.3665</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.3633</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.37228</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.45855</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.39185</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.37667</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.36617</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.37228</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.41025</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.41343</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.38585</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.3825</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.3677</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.36147</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.3858</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.40265</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.38327</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.39299</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.40562</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.41087</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.39293</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35143</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.37939</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.35071</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.34285</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.38402</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.27328</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.40698</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.5594</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.21295</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.27273</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.36811</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.42838</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.36918</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.40555</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.40584</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.48856</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.43132</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.06747</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.1614</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.15769</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29448</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.36033</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.36183</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.35846</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.36131</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.38663</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.40537</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.41237</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.39067</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.44422</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.40458</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.44014</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.42379</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.47424</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.41443</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.4312</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.42255</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.42974</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.44699</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.4397</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.36489</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.40357</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.38284</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.42351</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36651</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.39785</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.36806</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.42414</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.42489</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.39248</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.40204</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.44055</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.42412</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.39992</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.36049</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.54271</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.42001</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.43479</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.42922</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.40709</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.41398</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.3902</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.4617</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.37743</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.43819</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.43393</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.38998</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.44115</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.37791</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35777</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.38923</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.41529</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.36922</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.37878</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.37155</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.37362</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.37913</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.38463</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.40386</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.39013</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.40248</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.40799</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.41217</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.34739</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.35405</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.32049</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.40637</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.35661</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.34822</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.32004</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.32875</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.26973</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.29099</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.21311</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.29774</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.23546</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.23473</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.18981</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.33521</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.31055</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.35593</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.24312</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.0526</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.29402</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.27618</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.1419</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.16245</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.30297</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31298</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.31029</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.21603</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.24584</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.26604</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.22706</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27637</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28524</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.29588</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.34766</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.33787</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.36566</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.3587</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35927</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.39484</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.36502</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.38711</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.35181</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.40715</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.42159</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.3749</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.40552</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.37611</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.40368</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.37579</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.40848</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.43021</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.40458</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.37669</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.39525</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.4015</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.36063</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.3873</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.40073</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.41318</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.36314</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.37857</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.35968</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.37887</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.36991</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.33647</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.35238</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.35155</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.3488</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.35372</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.34921</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.38182</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.3460299999999999</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.34087</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.32572</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.36134</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.32697</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.32819</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.32631</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.35446</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.36583</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.36343</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.36342</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.35883</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.35883</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.36158</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.32298</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.36029</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.35883</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.35928</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.33228</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.36605</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.36574</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.33763</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.36957</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.24849</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.27774</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.29889</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.02211</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00044</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.00037</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04957</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.14809</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02108</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03957</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01505</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04283</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04071</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04858</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04823</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02921</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04939</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00079</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27467</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04964</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.0493</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03803</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01714</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03601</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20251</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26527</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.28912</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27991</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.31699</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.31784</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.3653</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.32298</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.34559</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.3557</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.34846</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.35752</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.32454</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.37053</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.36681</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.35157</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.36339</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.35965</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.38856</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.47023</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.36915</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.3932</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.36539</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.36196</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.36246</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.35677</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.36213</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.32264</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.36158</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.92226</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.78043</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.42846</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.62224</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.44833</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.4672</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.49052</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.39912</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.4085299999999999</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.34958</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.37843</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.38502</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.44041</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.37545</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.35176</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.45674</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.38637</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.43956</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.4126</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.45238</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.41969</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.42507</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.4421</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.47436</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.44736</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.43665</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.37214</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.35701</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.40967</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.43083</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.03508</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.08295</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.887</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.8483099999999999</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32499</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.39353</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.10163</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.13235</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.33529</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.16861</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.12898</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.15251</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.13414</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.31076</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.3533</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.09517</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.02447</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.11695</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.02139</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.30227</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.31595</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.12761</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.00638</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.12196</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.14945</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30116</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25468</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29196</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.4342</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32066</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32861</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.35545</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.39948</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.41525</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.35903</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.3885</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.3768</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.41687</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.90232</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.93264</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.9208500000000001</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.57294</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.98988</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.92743</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.92749</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.9491000000000001</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.85004</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.84823</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.85254</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.9495</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.9245</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.94502</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.9236</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.38365</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.37248</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.38331</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.38967</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.3895</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.52747</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.73448</v>
+      </c>
+      <c r="E138" t="n">
+        <v>1.01007</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.6889500000000001</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.5041600000000001</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.5331399999999999</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.45407</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.44857</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.39188</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.42321</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.43366</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.36713</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.37604</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.36341</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.57301</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.37708</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.38563</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.37005</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.37468</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.37987</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.43181</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.43004</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.41493</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.42853</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.53101</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.56186</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.42531</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.44642</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.33309</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.35675</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.35837</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.41153</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.38842</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.41726</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.37849</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.40387</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.36849</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.25433</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.25478</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.20055</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.36024</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.37851</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.34727</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.39792</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.40793</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31126</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.26184</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31405</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30514</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30523</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32682</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32331</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32087</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.40323</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31845</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31538</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31985</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32219</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.34425</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.34938</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33387</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32552</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.35185</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.35431</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.36504</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.35172</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.36405</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.37388</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.40819</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.40823</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.39618</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.3512</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.39323</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.39164</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.43697</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.53392</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.97117</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.45318</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.74515</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.5311399999999999</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.41116</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.48114</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.47246</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.43768</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.57096</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.38012</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.39081</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.36975</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.37617</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.36982</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.45772</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.46793</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.44538</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.43261</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.41854</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.41354</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.40871</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.38054</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.38804</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.37945</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.37909</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.35952</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.37186</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.36793</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.35507</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.37973</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.36017</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.35909</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.35429</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.35495</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.3559</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.35598</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.36889</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.35902</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.37861</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.36997</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.37932</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.36754</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.37951</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.47592</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.40079</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.38685</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.70056</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.8797699999999999</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.68243</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.82069</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.69128</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.5478500000000001</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.38279</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.37044</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.35677</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.35632</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.36868</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.36041</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.36637</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.40122</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30804</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.33929</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.30101</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33339</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.3465299999999999</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35155</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32589</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.3236</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.31341</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33049</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32905</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33357</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32292</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.35613</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.35282</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.42456</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.39715</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.47174</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.7454700000000001</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.82021</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.5014999999999999</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.44293</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.5218700000000001</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.54852</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.60773</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.82421</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.51551</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.82136</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.67876</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.5323099999999999</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.53337</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.43145</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.41989</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.46649</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.3842</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.37964</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.36621</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.47869</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.41314</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.3767799999999999</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.41385</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.38847</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.25848</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.38138</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36925</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.3771</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.35149</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.49109</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.41155</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.41384</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.40358</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.39571</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36791</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.38586</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37897</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.3885</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.38687</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.37917</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.37452</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.3685</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36679</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.3681</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36775</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.36364</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.33167</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.3647</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35846</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.35638</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.35617</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35418</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.37174</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.38114</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.38677</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36993</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.36499</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.3645</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.3633</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.36946</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.39437</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39138</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.37923</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43513</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.38009</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.37588</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.38748</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.36883</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31058</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36363</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.29555</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.38289</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.37191</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29258</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.32176</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.3297</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33799</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.3177</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31617</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33657</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34363</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32531</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33356</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34183</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33831</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32489</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34424</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.38947</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.3807</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.38485</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.3918</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.41188</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.38647</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.39191</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.43152</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.43329</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.74524</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.8278799999999999</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.69598</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.91161</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.0778</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.76619</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.52496</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.83558</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.7074900000000001</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.58028</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.23035</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.8547400000000001</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.5819</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.34642</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.23208</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.89075</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.4308999999999999</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.46472</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.40899</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.3814</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.3847</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.37526</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.38134</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.3126</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.37649</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.37256</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37537</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.36281</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.3534</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.35737</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.3687</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.35645</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.35654</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34624</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.41062</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.3563</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.34594</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.36709</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.36142</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.41787</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.3517</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.35533</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.35147</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.35915</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.34669</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.38259</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.37805</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.38898</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.38867</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.36628</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.3658</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.36278</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.3567</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.40234</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.34524</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.3677</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.37086</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.3562</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.33814</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.1998</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.28565</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.29586</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.18633</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.34377</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.33271</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.25271</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.13846</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.25892</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.07958</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.09201999999999999</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.29981</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.26928</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.11031</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.21935</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.13297</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.13915</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.14811</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.08227</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.29697</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.24346</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.20035</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.22053</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34802</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.34722</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.32233</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.36918</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.37683</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.36938</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.40828</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.38237</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.37076</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.38071</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.38181</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.3795</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.38265</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.37689</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.40446</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.52001</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.42682</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.43382</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.47995</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.45818</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.43782</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.40921</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.42773</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.40361</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.40801</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.42158</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.37999</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.44257</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.38842</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.38212</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.37635</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.36835</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.3901</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34258</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.09145</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.41571</v>
+      </c>
+      <c r="E142" t="n">
+        <v>1.18047</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.68059</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.45379</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.38444</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.77027</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.39039</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.4422</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.39135</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.38728</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.38715</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.38528</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.38115</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.39175</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38567</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.38442</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.38677</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.37598</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.3802</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.37923</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.37687</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.37603</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.36882</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.37449</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.36961</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.38954</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.37115</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.35777</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.36418</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.36963</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.37844</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.37703</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.36897</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.34816</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.38656</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.35544</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.41366</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.40848</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.29827</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.34184</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.38638</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.35805</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>1.47122</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.36809</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.35307</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.3212</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.34382</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.34962</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.6826100000000001</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>1.12695</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.35793</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.6561</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.52532</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.33065</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32225</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.3414700000000001</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.34933</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.3234</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.3571</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.39656</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.37565</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.40413</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.3905</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.40677</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.39813</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.39555</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.4547</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.41646</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.4132</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.3781</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39477</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.3933</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.37009</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.37135</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.40246</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.40349</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.39204</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.39906</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.38451</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.40229</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.40176</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.42593</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.38007</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.38283</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.41549</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.39983</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.40623</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.35937</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.37199</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.37122</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.37187</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.37331</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34811</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.4415</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.39785</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.40936</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37116</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.38908</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.38806</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.38557</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.38857</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.38024</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.38603</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.37545</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.3751</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.37353</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.37901</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.3722</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.37296</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.37759</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.37677</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.37124</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.37115</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.37029</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.3703</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.3731</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.36606</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.35156</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.37136</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.36281</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.31815</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31675</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.32374</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.1753</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30681</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29103</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31009</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14499</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19753</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.06572</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.27586</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.006690000000000001</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.05934</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.18407</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.12318</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.15374</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.15506</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.08914</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.20309</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.20038</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.17371</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22625</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.26431</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15564</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.30788</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30701</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.06815</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.30025</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.17372</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.19802</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.14481</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.27137</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.25598</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32059</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.30667</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.30987</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.31475</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.34251</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.35659</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.38683</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.35994</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.36756</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.37045</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.38794</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.38072</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.36819</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.37481</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.41288</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.38594</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.39259</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.39797</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.37099</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.39188</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.40821</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.39963</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.39061</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.41225</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.48779</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39539</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.40395</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.40065</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.40254</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.38105</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.39091</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.39619</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.39557</v>
       </c>
     </row>
   </sheetData>
